--- a/tests/regression_artifacts/downloads/email_TSCW18489131_budget_marine_grenada/current/INV000443447.xlsx
+++ b/tests/regression_artifacts/downloads/email_TSCW18489131_budget_marine_grenada/current/INV000443447.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM38"/>
+  <dimension ref="A1:AM37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>MARINE HARDWARE</t>
+          <t>Seats and furniture parts</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>OTHER APPARATUS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -908,7 +908,7 @@
       <c r="AJ3" s="2" t="n"/>
       <c r="AK3" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>OTHER APPARATUS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -991,7 +991,7 @@
       <c r="AJ4" s="2" t="n"/>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>OTHER APPARATUS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
       <c r="AJ5" s="2" t="n"/>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>OTHER APPARATUS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
       <c r="AJ6" s="2" t="n"/>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Other LUBRICANTS</t>
+          <t>LUBRICANTS</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27101990</t>
+          <t>27101900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
       <c r="AJ7" s="2" t="n"/>
       <c r="AK7" s="2" t="inlineStr">
         <is>
-          <t>27101990</t>
+          <t>27101900</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>OF OTHER PLASTICS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1572,7 +1572,7 @@
       <c r="AJ11" s="2" t="n"/>
       <c r="AK11" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>OF OTHER PLASTICS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
       <c r="AJ12" s="2" t="n"/>
       <c r="AK12" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>OF OTHER PLASTICS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1738,7 +1738,7 @@
       <c r="AJ13" s="2" t="n"/>
       <c r="AK13" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>OF OTHER PLASTICS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1821,7 +1821,7 @@
       <c r="AJ14" s="2" t="n"/>
       <c r="AK14" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>OF OTHER PLASTICS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
       <c r="AJ15" s="2" t="n"/>
       <c r="AK15" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>OF OTHER PLASTICS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1987,7 +1987,7 @@
       <c r="AJ16" s="2" t="n"/>
       <c r="AK16" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>OF OTHER PLASTICS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -2070,7 +2070,7 @@
       <c r="AJ17" s="2" t="n"/>
       <c r="AK17" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>OF OTHER PLASTICS</t>
+          <t>Other appliances</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
       <c r="AJ18" s="2" t="n"/>
       <c r="AK18" s="2" t="inlineStr">
         <is>
-          <t>84834090</t>
+          <t>84818000</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>CET (weighted avg 13.5%)</t>
+          <t>CET (weighted avg 12.6%)</t>
         </is>
       </c>
       <c r="K27" s="7" t="n"/>
@@ -2495,7 +2495,7 @@
       <c r="N27" s="7" t="n"/>
       <c r="O27" s="7" t="n"/>
       <c r="P27" s="9" t="n">
-        <v>924.02</v>
+        <v>858.76</v>
       </c>
       <c r="Q27" s="7" t="n"/>
       <c r="R27" s="7" t="n"/>
@@ -2531,7 +2531,7 @@
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 27101990: 20% CET (4% of value)</t>
+          <t xml:space="preserve">  └ 27101900: 20% CET (4% of value)</t>
         </is>
       </c>
       <c r="K28" s="7" t="n"/>
@@ -2576,7 +2576,7 @@
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 39172900: 20% CET (40% of value)</t>
+          <t xml:space="preserve">  └ 40169990: 20% CET (3% of value)</t>
         </is>
       </c>
       <c r="K29" s="7" t="n"/>
@@ -2585,7 +2585,7 @@
       <c r="N29" s="7" t="n"/>
       <c r="O29" s="7" t="n"/>
       <c r="P29" s="9" t="n">
-        <v>553.1900000000001</v>
+        <v>41.1</v>
       </c>
       <c r="Q29" s="7" t="n"/>
       <c r="R29" s="7" t="n"/>
@@ -2621,7 +2621,7 @@
       <c r="I30" s="7" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 39269090: 20% CET (9% of value)</t>
+          <t xml:space="preserve">  └ 73201090: 20% CET (0% of value)</t>
         </is>
       </c>
       <c r="K30" s="7" t="n"/>
@@ -2630,7 +2630,7 @@
       <c r="N30" s="7" t="n"/>
       <c r="O30" s="7" t="n"/>
       <c r="P30" s="9" t="n">
-        <v>124.34</v>
+        <v>1.27</v>
       </c>
       <c r="Q30" s="7" t="n"/>
       <c r="R30" s="7" t="n"/>
@@ -2666,7 +2666,7 @@
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 40169990: 20% CET (3% of value)</t>
+          <t xml:space="preserve">  └ 84818000: 5% CET (50% of value)</t>
         </is>
       </c>
       <c r="K31" s="7" t="n"/>
@@ -2675,7 +2675,7 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
       <c r="P31" s="9" t="n">
-        <v>41.1</v>
+        <v>169.38</v>
       </c>
       <c r="Q31" s="7" t="n"/>
       <c r="R31" s="7" t="n"/>
@@ -2711,7 +2711,7 @@
       <c r="I32" s="7" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 63079090: 0% CET (32% of value)</t>
+          <t xml:space="preserve">  └ 85365000: 20% CET (11% of value)</t>
         </is>
       </c>
       <c r="K32" s="7" t="n"/>
@@ -2720,7 +2720,7 @@
       <c r="N32" s="7" t="n"/>
       <c r="O32" s="7" t="n"/>
       <c r="P32" s="9" t="n">
-        <v>0</v>
+        <v>152.67</v>
       </c>
       <c r="Q32" s="7" t="n"/>
       <c r="R32" s="7" t="n"/>
@@ -2756,7 +2756,7 @@
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 73201090: 20% CET (0% of value)</t>
+          <t xml:space="preserve">  └ 94069090: 20% CET (32% of value)</t>
         </is>
       </c>
       <c r="K33" s="7" t="n"/>
@@ -2765,7 +2765,7 @@
       <c r="N33" s="7" t="n"/>
       <c r="O33" s="7" t="n"/>
       <c r="P33" s="9" t="n">
-        <v>1.27</v>
+        <v>442.88</v>
       </c>
       <c r="Q33" s="7" t="n"/>
       <c r="R33" s="7" t="n"/>
@@ -2801,7 +2801,7 @@
       <c r="I34" s="7" t="n"/>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 85365000: 20% CET (11% of value)</t>
+          <t>CSC (6%)</t>
         </is>
       </c>
       <c r="K34" s="7" t="n"/>
@@ -2810,7 +2810,7 @@
       <c r="N34" s="7" t="n"/>
       <c r="O34" s="7" t="n"/>
       <c r="P34" s="9" t="n">
-        <v>152.67</v>
+        <v>410.07</v>
       </c>
       <c r="Q34" s="7" t="n"/>
       <c r="R34" s="7" t="n"/>
@@ -2846,7 +2846,7 @@
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>CSC (6%)</t>
+          <t>VAT (15%) on CIF+CET+CSC</t>
         </is>
       </c>
       <c r="K35" s="7" t="n"/>
@@ -2855,7 +2855,7 @@
       <c r="N35" s="7" t="n"/>
       <c r="O35" s="7" t="n"/>
       <c r="P35" s="9" t="n">
-        <v>410.07</v>
+        <v>1215.5</v>
       </c>
       <c r="Q35" s="7" t="n"/>
       <c r="R35" s="7" t="n"/>
@@ -2880,139 +2880,94 @@
       <c r="AK35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n"/>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>VAT (15%) on CIF+CET+CSC</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="7" t="n"/>
-      <c r="P36" s="9" t="n">
-        <v>1225.29</v>
-      </c>
-      <c r="Q36" s="7" t="n"/>
-      <c r="R36" s="7" t="n"/>
-      <c r="S36" s="7" t="n"/>
-      <c r="T36" s="7" t="n"/>
-      <c r="U36" s="7" t="n"/>
-      <c r="V36" s="7" t="n"/>
-      <c r="W36" s="7" t="n"/>
-      <c r="X36" s="7" t="n"/>
-      <c r="Y36" s="7" t="n"/>
-      <c r="Z36" s="7" t="n"/>
-      <c r="AA36" s="7" t="n"/>
-      <c r="AB36" s="7" t="n"/>
-      <c r="AC36" s="7" t="n"/>
-      <c r="AD36" s="7" t="n"/>
-      <c r="AE36" s="7" t="n"/>
-      <c r="AF36" s="7" t="n"/>
-      <c r="AG36" s="7" t="n"/>
-      <c r="AH36" s="7" t="n"/>
-      <c r="AI36" s="7" t="n"/>
-      <c r="AJ36" s="7" t="n"/>
-      <c r="AK36" s="7" t="n"/>
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>ESTIMATED TOTAL DUTIES</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="n"/>
+      <c r="L36" s="10" t="n"/>
+      <c r="M36" s="10" t="n"/>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="11" t="n">
+        <v>2484.33</v>
+      </c>
+      <c r="Q36" s="10" t="n"/>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="10" t="n"/>
+      <c r="U36" s="10" t="n"/>
+      <c r="V36" s="10" t="n"/>
+      <c r="W36" s="10" t="n"/>
+      <c r="X36" s="10" t="n"/>
+      <c r="Y36" s="10" t="n"/>
+      <c r="Z36" s="10" t="n"/>
+      <c r="AA36" s="10" t="n"/>
+      <c r="AB36" s="10" t="n"/>
+      <c r="AC36" s="10" t="n"/>
+      <c r="AD36" s="10" t="n"/>
+      <c r="AE36" s="10" t="n"/>
+      <c r="AF36" s="10" t="n"/>
+      <c r="AG36" s="10" t="n"/>
+      <c r="AH36" s="10" t="n"/>
+      <c r="AI36" s="10" t="n"/>
+      <c r="AJ36" s="10" t="n"/>
+      <c r="AK36" s="10" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>ESTIMATED TOTAL DUTIES</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="10" t="n"/>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="11" t="n">
-        <v>2559.38</v>
-      </c>
-      <c r="Q37" s="10" t="n"/>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="10" t="n"/>
-      <c r="T37" s="10" t="n"/>
-      <c r="U37" s="10" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="10" t="n"/>
-      <c r="Y37" s="10" t="n"/>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="10" t="n"/>
-      <c r="AB37" s="10" t="n"/>
-      <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="10" t="n"/>
-      <c r="AF37" s="10" t="n"/>
-      <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
-      <c r="AK37" s="10" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n"/>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Effective Duty Rate</t>
         </is>
       </c>
-      <c r="K38" s="7" t="n"/>
-      <c r="L38" s="7" t="n"/>
-      <c r="M38" s="7" t="n"/>
-      <c r="N38" s="7" t="n"/>
-      <c r="O38" s="7" t="n"/>
-      <c r="P38" s="12" t="n">
-        <v>0.3744794791133221</v>
-      </c>
-      <c r="Q38" s="7" t="n"/>
-      <c r="R38" s="7" t="n"/>
-      <c r="S38" s="7" t="n"/>
-      <c r="T38" s="7" t="n"/>
-      <c r="U38" s="7" t="n"/>
-      <c r="V38" s="7" t="n"/>
-      <c r="W38" s="7" t="n"/>
-      <c r="X38" s="7" t="n"/>
-      <c r="Y38" s="7" t="n"/>
-      <c r="Z38" s="7" t="n"/>
-      <c r="AA38" s="7" t="n"/>
-      <c r="AB38" s="7" t="n"/>
-      <c r="AC38" s="7" t="n"/>
-      <c r="AD38" s="7" t="n"/>
-      <c r="AE38" s="7" t="n"/>
-      <c r="AF38" s="7" t="n"/>
-      <c r="AG38" s="7" t="n"/>
-      <c r="AH38" s="7" t="n"/>
-      <c r="AI38" s="7" t="n"/>
-      <c r="AJ38" s="7" t="n"/>
-      <c r="AK38" s="7" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+      <c r="P37" s="12" t="n">
+        <v>0.3634984270978125</v>
+      </c>
+      <c r="Q37" s="7" t="n"/>
+      <c r="R37" s="7" t="n"/>
+      <c r="S37" s="7" t="n"/>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
+      <c r="W37" s="7" t="n"/>
+      <c r="X37" s="7" t="n"/>
+      <c r="Y37" s="7" t="n"/>
+      <c r="Z37" s="7" t="n"/>
+      <c r="AA37" s="7" t="n"/>
+      <c r="AB37" s="7" t="n"/>
+      <c r="AC37" s="7" t="n"/>
+      <c r="AD37" s="7" t="n"/>
+      <c r="AE37" s="7" t="n"/>
+      <c r="AF37" s="7" t="n"/>
+      <c r="AG37" s="7" t="n"/>
+      <c r="AH37" s="7" t="n"/>
+      <c r="AI37" s="7" t="n"/>
+      <c r="AJ37" s="7" t="n"/>
+      <c r="AK37" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
